--- a/experiment/ELAN_bestx4/Test/results-Urban100/Urban100.xlsx
+++ b/experiment/ELAN_bestx4/Test/results-Urban100/Urban100.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27.69</v>
+        <v>27.74</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7685</v>
+        <v>0.7701</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26.87</v>
+        <v>26.93</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8205</v>
+        <v>0.8233</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.95</v>
+        <v>24.01</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6916</v>
+        <v>0.6943</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.3</v>
+        <v>23.28</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8367</v>
+        <v>0.8373</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28.21</v>
+        <v>28.29</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9509</v>
+        <v>0.9520999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22.62</v>
+        <v>22.65</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6319</v>
+        <v>0.6333</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29.62</v>
+        <v>29.7</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8633999999999999</v>
+        <v>0.8651</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21.65</v>
+        <v>21.68</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6704</v>
+        <v>0.6735</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>34.28</v>
+        <v>34.33</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9317</v>
+        <v>0.9322</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27.5</v>
+        <v>27.59</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8913</v>
+        <v>0.8932</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17.83</v>
+        <v>17.8</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7872</v>
+        <v>0.7896</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24.02</v>
+        <v>24.07</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7421</v>
+        <v>0.7457</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>29.66</v>
+        <v>29.72</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8421999999999999</v>
+        <v>0.8438</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22.49</v>
+        <v>22.53</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6935</v>
+        <v>0.6962</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>26.27</v>
+        <v>26.35</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7403999999999999</v>
+        <v>0.7425</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>30.6</v>
+        <v>30.57</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9159</v>
+        <v>0.9163</v>
       </c>
     </row>
     <row r="18">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25.9</v>
+        <v>25.97</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8328</v>
+        <v>0.8347</v>
       </c>
     </row>
     <row r="19">
@@ -676,7 +676,7 @@
         <v>26.41</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7171999999999999</v>
+        <v>0.7177</v>
       </c>
     </row>
     <row r="20">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>22.44</v>
+        <v>22.57</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8207</v>
+        <v>0.8242</v>
       </c>
     </row>
     <row r="21">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22.26</v>
+        <v>22.31</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7229</v>
+        <v>0.7256</v>
       </c>
     </row>
     <row r="22">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>29.77</v>
+        <v>29.78</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7875</v>
+        <v>0.7884</v>
       </c>
     </row>
     <row r="23">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>26.14</v>
+        <v>26.16</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7629</v>
+        <v>0.764</v>
       </c>
     </row>
     <row r="24">
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>30.63</v>
+        <v>30.74</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9189000000000001</v>
+        <v>0.9202</v>
       </c>
     </row>
     <row r="25">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>20.78</v>
+        <v>20.94</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6862</v>
+        <v>0.6961000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>31.78</v>
+        <v>31.96</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8985</v>
+        <v>0.9006999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>28.1</v>
+        <v>28.12</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7034</v>
+        <v>0.7059</v>
       </c>
     </row>
     <row r="28">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28.46</v>
+        <v>28.51</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8013</v>
+        <v>0.8027</v>
       </c>
     </row>
     <row r="29">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>31.67</v>
+        <v>31.75</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8796</v>
+        <v>0.8808</v>
       </c>
     </row>
     <row r="30">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>27.33</v>
+        <v>27.4</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8705000000000001</v>
+        <v>0.8723</v>
       </c>
     </row>
     <row r="31">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>24.85</v>
+        <v>24.99</v>
       </c>
       <c r="C31" t="n">
-        <v>0.8171</v>
+        <v>0.8224</v>
       </c>
     </row>
     <row r="32">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>24.33</v>
+        <v>24.37</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7932</v>
+        <v>0.7955</v>
       </c>
     </row>
     <row r="33">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>29.33</v>
+        <v>29.3</v>
       </c>
       <c r="C33" t="n">
-        <v>0.8619</v>
+        <v>0.8621</v>
       </c>
     </row>
     <row r="34">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>27.43</v>
+        <v>27.56</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8096</v>
+        <v>0.8128</v>
       </c>
     </row>
     <row r="35">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>23.16</v>
+        <v>23.21</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5907</v>
+        <v>0.593</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>29.1</v>
+        <v>29.33</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8764999999999999</v>
+        <v>0.8806</v>
       </c>
     </row>
     <row r="37">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>28.97</v>
+        <v>28.94</v>
       </c>
       <c r="C37" t="n">
-        <v>0.8885</v>
+        <v>0.889</v>
       </c>
     </row>
     <row r="38">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>26.68</v>
+        <v>26.72</v>
       </c>
       <c r="C38" t="n">
-        <v>0.8052</v>
+        <v>0.8065</v>
       </c>
     </row>
     <row r="39">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>27.29</v>
+        <v>27.33</v>
       </c>
       <c r="C39" t="n">
-        <v>0.6947</v>
+        <v>0.6965</v>
       </c>
     </row>
     <row r="40">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>23.22</v>
+        <v>23.26</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7556</v>
+        <v>0.7579</v>
       </c>
     </row>
     <row r="41">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>26.64</v>
+        <v>26.66</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9358</v>
+        <v>0.9366</v>
       </c>
     </row>
     <row r="42">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>26.71</v>
+        <v>26.75</v>
       </c>
       <c r="C42" t="n">
-        <v>0.8861</v>
+        <v>0.8878</v>
       </c>
     </row>
     <row r="43">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>29.07</v>
+        <v>29.13</v>
       </c>
       <c r="C43" t="n">
-        <v>0.8897</v>
+        <v>0.8912</v>
       </c>
     </row>
     <row r="44">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>32</v>
+        <v>32.24</v>
       </c>
       <c r="C44" t="n">
-        <v>0.9329</v>
+        <v>0.9338</v>
       </c>
     </row>
     <row r="45">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>32.16</v>
+        <v>32.25</v>
       </c>
       <c r="C45" t="n">
-        <v>0.8728</v>
+        <v>0.8743</v>
       </c>
     </row>
     <row r="46">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>24.24</v>
+        <v>24.35</v>
       </c>
       <c r="C46" t="n">
-        <v>0.7201</v>
+        <v>0.7221</v>
       </c>
     </row>
     <row r="47">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>23.76</v>
+        <v>23.82</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7645999999999999</v>
+        <v>0.768</v>
       </c>
     </row>
     <row r="48">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>22.18</v>
+        <v>22.25</v>
       </c>
       <c r="C48" t="n">
-        <v>0.7831</v>
+        <v>0.7873</v>
       </c>
     </row>
     <row r="49">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>20.69</v>
+        <v>20.77</v>
       </c>
       <c r="C49" t="n">
-        <v>0.8263</v>
+        <v>0.8298</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>23.69</v>
+        <v>23.75</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7554999999999999</v>
+        <v>0.7593</v>
       </c>
     </row>
     <row r="51">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>25.48</v>
+        <v>25.53</v>
       </c>
       <c r="C51" t="n">
-        <v>0.7784</v>
+        <v>0.7808</v>
       </c>
     </row>
     <row r="52">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>27.51</v>
+        <v>27.59</v>
       </c>
       <c r="C52" t="n">
-        <v>0.8506</v>
+        <v>0.8525</v>
       </c>
     </row>
     <row r="53">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>28.98</v>
+        <v>29.05</v>
       </c>
       <c r="C53" t="n">
-        <v>0.9088000000000001</v>
+        <v>0.9102</v>
       </c>
     </row>
     <row r="54">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>22.56</v>
+        <v>22.61</v>
       </c>
       <c r="C54" t="n">
-        <v>0.7363</v>
+        <v>0.739</v>
       </c>
     </row>
     <row r="55">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>21.31</v>
+        <v>21.35</v>
       </c>
       <c r="C55" t="n">
-        <v>0.6563</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="56">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>33.04</v>
+        <v>33.29</v>
       </c>
       <c r="C56" t="n">
-        <v>0.9459</v>
+        <v>0.9473</v>
       </c>
     </row>
     <row r="57">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25.13</v>
+        <v>25.22</v>
       </c>
       <c r="C57" t="n">
-        <v>0.7877</v>
+        <v>0.791</v>
       </c>
     </row>
     <row r="58">
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>31.26</v>
+        <v>31.36</v>
       </c>
       <c r="C58" t="n">
-        <v>0.9002</v>
+        <v>0.9022</v>
       </c>
     </row>
     <row r="59">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>26.12</v>
+        <v>26.22</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8646</v>
+        <v>0.8671</v>
       </c>
     </row>
     <row r="60">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>22.36</v>
+        <v>22.46</v>
       </c>
       <c r="C60" t="n">
-        <v>0.7704</v>
+        <v>0.7744</v>
       </c>
     </row>
     <row r="61">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>22.64</v>
+        <v>22.66</v>
       </c>
       <c r="C61" t="n">
-        <v>0.5733</v>
+        <v>0.5752</v>
       </c>
     </row>
     <row r="62">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>24.89</v>
+        <v>24.94</v>
       </c>
       <c r="C62" t="n">
-        <v>0.763</v>
+        <v>0.7664</v>
       </c>
     </row>
     <row r="63">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>21.99</v>
+        <v>22.16</v>
       </c>
       <c r="C63" t="n">
-        <v>0.8208</v>
+        <v>0.8274</v>
       </c>
     </row>
     <row r="64">
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>22.49</v>
+        <v>22.55</v>
       </c>
       <c r="C64" t="n">
-        <v>0.6238</v>
+        <v>0.6251</v>
       </c>
     </row>
     <row r="65">
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>26.74</v>
+        <v>26.77</v>
       </c>
       <c r="C65" t="n">
-        <v>0.7892</v>
+        <v>0.7911</v>
       </c>
     </row>
     <row r="66">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>25.53</v>
+        <v>25.57</v>
       </c>
       <c r="C66" t="n">
-        <v>0.7296</v>
+        <v>0.7322</v>
       </c>
     </row>
     <row r="67">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>22.32</v>
+        <v>22.35</v>
       </c>
       <c r="C67" t="n">
-        <v>0.6489</v>
+        <v>0.6501</v>
       </c>
     </row>
     <row r="68">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>20.4</v>
+        <v>20.42</v>
       </c>
       <c r="C68" t="n">
-        <v>0.8869</v>
+        <v>0.8885999999999999</v>
       </c>
     </row>
     <row r="69">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>30.41</v>
+        <v>30.52</v>
       </c>
       <c r="C69" t="n">
-        <v>0.8861</v>
+        <v>0.8882</v>
       </c>
     </row>
     <row r="70">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>24.9</v>
+        <v>24.92</v>
       </c>
       <c r="C70" t="n">
-        <v>0.7575</v>
+        <v>0.7589</v>
       </c>
     </row>
     <row r="71">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>22.21</v>
+        <v>22.24</v>
       </c>
       <c r="C71" t="n">
-        <v>0.5996</v>
+        <v>0.6012</v>
       </c>
     </row>
     <row r="72">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>28.13</v>
+        <v>28.18</v>
       </c>
       <c r="C72" t="n">
-        <v>0.6711</v>
+        <v>0.6739000000000001</v>
       </c>
     </row>
     <row r="73">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>20.46</v>
+        <v>20.57</v>
       </c>
       <c r="C73" t="n">
-        <v>0.8244</v>
+        <v>0.829</v>
       </c>
     </row>
     <row r="74">
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>20.47</v>
+        <v>20.41</v>
       </c>
       <c r="C74" t="n">
-        <v>0.5873</v>
+        <v>0.5894</v>
       </c>
     </row>
     <row r="75">
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>23.91</v>
+        <v>23.99</v>
       </c>
       <c r="C75" t="n">
-        <v>0.7206</v>
+        <v>0.7255</v>
       </c>
     </row>
     <row r="76">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>31.84</v>
+        <v>31.96</v>
       </c>
       <c r="C76" t="n">
-        <v>0.8869</v>
+        <v>0.8887</v>
       </c>
     </row>
     <row r="77">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>23.33</v>
+        <v>23.45</v>
       </c>
       <c r="C77" t="n">
-        <v>0.7471</v>
+        <v>0.7538</v>
       </c>
     </row>
     <row r="78">
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>22.78</v>
+        <v>22.8</v>
       </c>
       <c r="C78" t="n">
-        <v>0.6773</v>
+        <v>0.679</v>
       </c>
     </row>
     <row r="79">
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>27.66</v>
+        <v>27.74</v>
       </c>
       <c r="C79" t="n">
-        <v>0.7799</v>
+        <v>0.7819</v>
       </c>
     </row>
     <row r="80">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>25.51</v>
+        <v>25.57</v>
       </c>
       <c r="C80" t="n">
-        <v>0.7008</v>
+        <v>0.7027</v>
       </c>
     </row>
     <row r="81">
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>35.68</v>
+        <v>35.67</v>
       </c>
       <c r="C81" t="n">
-        <v>0.9529</v>
+        <v>0.9530999999999999</v>
       </c>
     </row>
     <row r="82">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>37.31</v>
+        <v>37.53</v>
       </c>
       <c r="C82" t="n">
-        <v>0.9698</v>
+        <v>0.9708</v>
       </c>
     </row>
     <row r="83">
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>32.89</v>
+        <v>32.9</v>
       </c>
       <c r="C83" t="n">
         <v>0.9412</v>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>22.37</v>
+        <v>22.43</v>
       </c>
       <c r="C84" t="n">
-        <v>0.7036</v>
+        <v>0.7079</v>
       </c>
     </row>
     <row r="85">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>28.88</v>
+        <v>28.94</v>
       </c>
       <c r="C85" t="n">
-        <v>0.8164</v>
+        <v>0.8179</v>
       </c>
     </row>
     <row r="86">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>28.43</v>
+        <v>28.55</v>
       </c>
       <c r="C86" t="n">
-        <v>0.9038</v>
+        <v>0.9064</v>
       </c>
     </row>
     <row r="87">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>30.63</v>
+        <v>30.64</v>
       </c>
       <c r="C87" t="n">
-        <v>0.8894</v>
+        <v>0.8901</v>
       </c>
     </row>
     <row r="88">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>27.94</v>
+        <v>28.1</v>
       </c>
       <c r="C88" t="n">
-        <v>0.8867</v>
+        <v>0.8893</v>
       </c>
     </row>
     <row r="89">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>20.01</v>
+        <v>20.04</v>
       </c>
       <c r="C89" t="n">
-        <v>0.5762</v>
+        <v>0.5793</v>
       </c>
     </row>
     <row r="90">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>26.83</v>
+        <v>26.86</v>
       </c>
       <c r="C90" t="n">
-        <v>0.7198</v>
+        <v>0.7217</v>
       </c>
     </row>
     <row r="91">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>38.52</v>
+        <v>38.78</v>
       </c>
       <c r="C91" t="n">
-        <v>0.9765</v>
+        <v>0.9772</v>
       </c>
     </row>
     <row r="92">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>24.11</v>
+        <v>24.17</v>
       </c>
       <c r="C92" t="n">
-        <v>0.6886</v>
+        <v>0.6925</v>
       </c>
     </row>
     <row r="93">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>19.13</v>
+        <v>19.14</v>
       </c>
       <c r="C93" t="n">
-        <v>0.6624</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="94">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>29.6</v>
+        <v>29.64</v>
       </c>
       <c r="C94" t="n">
-        <v>0.9291</v>
+        <v>0.9297</v>
       </c>
     </row>
     <row r="95">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>27.28</v>
+        <v>27.33</v>
       </c>
       <c r="C95" t="n">
-        <v>0.7875</v>
+        <v>0.7896</v>
       </c>
     </row>
     <row r="96">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>20.27</v>
+        <v>20.33</v>
       </c>
       <c r="C96" t="n">
-        <v>0.4551</v>
+        <v>0.4605</v>
       </c>
     </row>
     <row r="97">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>25.88</v>
+        <v>25.87</v>
       </c>
       <c r="C97" t="n">
-        <v>0.8767</v>
+        <v>0.8779</v>
       </c>
     </row>
     <row r="98">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>24.94</v>
+        <v>25.01</v>
       </c>
       <c r="C98" t="n">
-        <v>0.7661</v>
+        <v>0.7699</v>
       </c>
     </row>
     <row r="99">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>20.78</v>
+        <v>20.82</v>
       </c>
       <c r="C99" t="n">
-        <v>0.5373</v>
+        <v>0.5421</v>
       </c>
     </row>
     <row r="100">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>25.91</v>
+        <v>26.13</v>
       </c>
       <c r="C100" t="n">
-        <v>0.8006</v>
+        <v>0.8062</v>
       </c>
     </row>
     <row r="101">
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>26.26</v>
+        <v>26.28</v>
       </c>
       <c r="C101" t="n">
-        <v>0.7472</v>
+        <v>0.7483</v>
       </c>
     </row>
     <row r="102">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>26.2</v>
+        <v>26.27</v>
       </c>
       <c r="C102" t="n">
-        <v>0.789</v>
+        <v>0.7914</v>
       </c>
     </row>
   </sheetData>
